--- a/guia-1/reto-2/Reto2.xlsx
+++ b/guia-1/reto-2/Reto2.xlsx
@@ -10885,115 +10885,115 @@
         <v>0</v>
       </c>
       <c r="AH66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B2:D4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B2:D4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C2:E4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C2:E4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D2:F4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D2:F4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E2:G4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E2:G4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F2:H4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F2:H4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G2:I4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G2:I4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H2:J4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H2:J4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I2:K4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I2:K4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J2:L4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J2:L4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K2:M4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K2:M4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L2:N4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L2:N4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M2:O4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M2:O4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N2:P4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N2:P4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O2:Q4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O2:Q4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P2:R4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P2:R4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AW66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q2:S4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q2:S4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AX66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R2:T4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R2:T4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S2:U4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S2:U4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T2:V4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T2:V4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U2:W4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U2:W4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V2:X4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V2:X4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W2:Y4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W2:Y4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X2:Z4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X2:Z4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y2:AA4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y2:AA4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z2:AB4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z2:AB4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA2:AC4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA2:AC4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB2:AD4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB2:AD4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI66" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC2:AE4,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC2:AE4,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -11111,115 +11111,115 @@
         <v>0</v>
       </c>
       <c r="AH67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B3:D5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B3:D5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C3:E5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C3:E5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D3:F5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D3:F5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E3:G5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E3:G5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F3:H5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F3:H5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G3:I5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G3:I5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H3:J5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H3:J5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I3:K5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I3:K5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J3:L5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J3:L5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K3:M5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K3:M5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L3:N5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L3:N5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M3:O5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M3:O5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N3:P5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N3:P5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O3:Q5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O3:Q5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P3:R5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P3:R5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AW67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q3:S5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q3:S5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AX67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R3:T5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R3:T5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S3:U5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S3:U5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T3:V5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T3:V5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U3:W5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U3:W5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V3:X5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V3:X5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W3:Y5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W3:Y5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X3:Z5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X3:Z5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y3:AA5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y3:AA5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z3:AB5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z3:AB5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA3:AC5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA3:AC5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB3:AD5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB3:AD5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI67" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC3:AE5,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC3:AE5,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -11337,115 +11337,115 @@
         <v>0</v>
       </c>
       <c r="AH68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B4:D6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B4:D6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C4:E6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C4:E6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D4:F6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D4:F6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E4:G6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E4:G6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F4:H6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F4:H6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G4:I6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G4:I6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H4:J6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H4:J6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I4:K6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I4:K6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J4:L6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J4:L6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K4:M6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K4:M6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L4:N6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L4:N6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M4:O6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M4:O6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N4:P6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N4:P6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O4:Q6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O4:Q6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P4:R6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P4:R6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AW68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q4:S6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q4:S6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AX68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R4:T6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R4:T6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S4:U6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S4:U6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T4:V6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T4:V6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U4:W6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U4:W6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V4:X6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V4:X6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W4:Y6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W4:Y6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X4:Z6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X4:Z6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y4:AA6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y4:AA6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z4:AB6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z4:AB6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA4:AC6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA4:AC6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB4:AD6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB4:AD6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI68" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC4:AE6,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC4:AE6,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -11563,115 +11563,115 @@
         <v>0</v>
       </c>
       <c r="AH69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B5:D7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B5:D7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C5:E7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C5:E7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D5:F7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D5:F7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E5:G7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E5:G7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F5:H7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F5:H7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G5:I7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G5:I7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H5:J7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H5:J7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I5:K7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I5:K7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J5:L7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J5:L7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K5:M7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K5:M7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L5:N7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L5:N7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M5:O7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M5:O7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N5:P7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N5:P7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O5:Q7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O5:Q7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P5:R7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P5:R7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AW69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q5:S7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q5:S7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AX69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R5:T7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R5:T7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S5:U7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S5:U7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T5:V7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T5:V7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U5:W7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U5:W7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V5:X7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V5:X7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W5:Y7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W5:Y7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X5:Z7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X5:Z7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y5:AA7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y5:AA7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z5:AB7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z5:AB7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA5:AC7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA5:AC7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB5:AD7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB5:AD7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI69" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC5:AE7,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC5:AE7,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -11789,115 +11789,115 @@
         <v>0</v>
       </c>
       <c r="AH70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B6:D8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B6:D8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C6:E8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C6:E8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D6:F8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D6:F8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E6:G8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E6:G8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F6:H8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F6:H8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G6:I8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G6:I8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H6:J8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H6:J8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I6:K8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I6:K8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J6:L8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J6:L8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K6:M8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K6:M8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L6:N8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L6:N8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M6:O8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M6:O8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N6:P8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N6:P8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O6:Q8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O6:Q8,$AK$9:$AM$11)/$AK$13))</f>
         <v>95.625</v>
       </c>
       <c r="AV70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P6:R8,$AK$9:$AM$11)/$AK$13</f>
-        <v>-63.75</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P6:R8,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AW70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q6:S8,$AK$9:$AM$11)/$AK$13</f>
-        <v>-47.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q6:S8,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AX70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R6:T8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R6:T8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S6:U8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S6:U8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T6:V8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T6:V8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U6:W8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U6:W8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V6:X8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V6:X8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W6:Y8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W6:Y8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X6:Z8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X6:Z8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y6:AA8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y6:AA8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z6:AB8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z6:AB8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA6:AC8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA6:AC8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB6:AD8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB6:AD8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI70" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC6:AE8,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC6:AE8,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -12015,115 +12015,115 @@
         <v>0</v>
       </c>
       <c r="AH71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B7:D9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B7:D9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C7:E9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C7:E9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D7:F9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D7:F9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK71" s="13" t="e">
-        <f aca="false">SUMPRODUCT(E7:G9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E7:G9,$AK$9:$AM$11)/$AK$13))</f>
         <v>#NAME?</v>
       </c>
       <c r="AL71" s="13" t="e">
-        <f aca="false">SUMPRODUCT(F7:H9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F7:H9,$AK$9:$AM$11)/$AK$13))</f>
         <v>#NAME?</v>
       </c>
       <c r="AM71" s="13" t="e">
-        <f aca="false">SUMPRODUCT(G7:I9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G7:I9,$AK$9:$AM$11)/$AK$13))</f>
         <v>#NAME?</v>
       </c>
       <c r="AN71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H7:J9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H7:J9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I7:K9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I7:K9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J7:L9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J7:L9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K7:M9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K7:M9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L7:N9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L7:N9,$AK$9:$AM$11)/$AK$13))</f>
         <v>95.625</v>
       </c>
       <c r="AS71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M7:O9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M7:O9,$AK$9:$AM$11)/$AK$13))</f>
         <v>31.875</v>
       </c>
       <c r="AT71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N7:P9,$AK$9:$AM$11)/$AK$13</f>
-        <v>-15.9375</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N7:P9,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AU71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O7:Q9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O7:Q9,$AK$9:$AM$11)/$AK$13))</f>
         <v>63.75</v>
       </c>
       <c r="AV71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P7:R9,$AK$9:$AM$11)/$AK$13</f>
-        <v>-159.375</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P7:R9,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AW71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q7:S9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q7:S9,$AK$9:$AM$11)/$AK$13))</f>
         <v>95.625</v>
       </c>
       <c r="AX71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R7:T9,$AK$9:$AM$11)/$AK$13</f>
-        <v>-15.9375</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R7:T9,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AY71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S7:U9,$AK$9:$AM$11)/$AK$13</f>
-        <v>-111.5625</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S7:U9,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AZ71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T7:V9,$AK$9:$AM$11)/$AK$13</f>
-        <v>-47.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T7:V9,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="BA71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U7:W9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U7:W9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V7:X9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V7:X9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W7:Y9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W7:Y9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X7:Z9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X7:Z9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y7:AA9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y7:AA9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z7:AB9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z7:AB9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA7:AC9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA7:AC9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB7:AD9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB7:AD9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI71" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC7:AE9,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC7:AE9,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -12241,115 +12241,115 @@
         <v>0</v>
       </c>
       <c r="AH72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B8:D10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B8:D10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C8:E10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C8:E10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D8:F10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D8:F10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK72" s="13" t="e">
-        <f aca="false">SUMPRODUCT(E8:G10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E8:G10,$AK$9:$AM$11)/$AK$13))</f>
         <v>#NAME?</v>
       </c>
       <c r="AL72" s="13" t="e">
-        <f aca="false">SUMPRODUCT(F8:H10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F8:H10,$AK$9:$AM$11)/$AK$13))</f>
         <v>#NAME?</v>
       </c>
       <c r="AM72" s="13" t="e">
-        <f aca="false">SUMPRODUCT(G8:I10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G8:I10,$AK$9:$AM$11)/$AK$13))</f>
         <v>#NAME?</v>
       </c>
       <c r="AN72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H8:J10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H8:J10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I8:K10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I8:K10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J8:L10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J8:L10,$AK$9:$AM$11)/$AK$13))</f>
         <v>95.625</v>
       </c>
       <c r="AQ72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K8:M10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K8:M10,$AK$9:$AM$11)/$AK$13))</f>
         <v>31.875</v>
       </c>
       <c r="AR72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L8:N10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L8:N10,$AK$9:$AM$11)/$AK$13))</f>
         <v>63.75</v>
       </c>
       <c r="AS72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M8:O10,$AK$9:$AM$11)/$AK$13</f>
-        <v>-79.6875</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M8:O10,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AT72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N8:P10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N8:P10,$AK$9:$AM$11)/$AK$13))</f>
         <v>31.875</v>
       </c>
       <c r="AU72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O8:Q10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O8:Q10,$AK$9:$AM$11)/$AK$13))</f>
         <v>31.875</v>
       </c>
       <c r="AV72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P8:R10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P8:R10,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AW72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q8:S10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q8:S10,$AK$9:$AM$11)/$AK$13))</f>
         <v>111.5625</v>
       </c>
       <c r="AX72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R8:T10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R8:T10,$AK$9:$AM$11)/$AK$13))</f>
         <v>31.875</v>
       </c>
       <c r="AY72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S8:U10,$AK$9:$AM$11)/$AK$13</f>
-        <v>-47.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S8:U10,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AZ72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T8:V10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T8:V10,$AK$9:$AM$11)/$AK$13))</f>
         <v>95.625</v>
       </c>
       <c r="BA72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U8:W10,$AK$9:$AM$11)/$AK$13</f>
-        <v>-111.5625</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U8:W10,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="BB72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V8:X10,$AK$9:$AM$11)/$AK$13</f>
-        <v>-47.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V8:X10,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="BC72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W8:Y10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W8:Y10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X8:Z10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X8:Z10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y8:AA10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y8:AA10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z8:AB10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z8:AB10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA8:AC10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA8:AC10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB8:AD10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB8:AD10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI72" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC8:AE10,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC8:AE10,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -12467,115 +12467,115 @@
         <v>0</v>
       </c>
       <c r="AH73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B9:D11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B9:D11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C9:E11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C9:E11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D9:F11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D9:F11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK73" s="13" t="e">
-        <f aca="false">SUMPRODUCT(E9:G11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E9:G11,$AK$9:$AM$11)/$AK$13))</f>
         <v>#NAME?</v>
       </c>
       <c r="AL73" s="13" t="e">
-        <f aca="false">SUMPRODUCT(F9:H11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F9:H11,$AK$9:$AM$11)/$AK$13))</f>
         <v>#NAME?</v>
       </c>
       <c r="AM73" s="13" t="e">
-        <f aca="false">SUMPRODUCT(G9:I11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G9:I11,$AK$9:$AM$11)/$AK$13))</f>
         <v>#NAME?</v>
       </c>
       <c r="AN73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H9:J11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H9:J11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I9:K11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I9:K11,$AK$9:$AM$11)/$AK$13))</f>
         <v>95.625</v>
       </c>
       <c r="AP73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J9:L11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J9:L11,$AK$9:$AM$11)/$AK$13))</f>
         <v>111.5625</v>
       </c>
       <c r="AQ73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K9:M11,$AK$9:$AM$11)/$AK$13</f>
-        <v>-79.6875</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K9:M11,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AR73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L9:N11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L9:N11,$AK$9:$AM$11)/$AK$13))</f>
         <v>31.875</v>
       </c>
       <c r="AS73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M9:O11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M9:O11,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AT73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N9:P11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N9:P11,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O9:Q11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O9:Q11,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P9:R11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P9:R11,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q9:S11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q9:S11,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R9:T11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R9:T11,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S9:U11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S9:U11,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T9:V11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T9:V11,$AK$9:$AM$11)/$AK$13))</f>
         <v>111.5625</v>
       </c>
       <c r="BA73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U9:W11,$AK$9:$AM$11)/$AK$13</f>
-        <v>-47.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U9:W11,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="BB73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V9:X11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V9:X11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W9:Y11,$AK$9:$AM$11)/$AK$13</f>
-        <v>-47.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W9:Y11,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="BD73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X9:Z11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X9:Z11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y9:AA11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y9:AA11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z9:AB11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z9:AB11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA9:AC11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA9:AC11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB9:AD11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB9:AD11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI73" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC9:AE11,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC9:AE11,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -12693,115 +12693,115 @@
         <v>0</v>
       </c>
       <c r="AH74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B10:D12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B10:D12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C10:E12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C10:E12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D10:F12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D10:F12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E10:G12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E10:G12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F10:H12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F10:H12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G10:I12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G10:I12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H10:J12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H10:J12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I10:K12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I10:K12,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AP74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J10:L12,$AK$9:$AM$11)/$AK$13</f>
-        <v>-31.875</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J10:L12,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AQ74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K10:M12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K10:M12,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AR74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L10:N12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L10:N12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M10:O12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M10:O12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N10:P12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N10:P12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O10:Q12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O10:Q12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P10:R12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P10:R12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q10:S12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q10:S12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R10:T12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R10:T12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S10:U12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S10:U12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T10:V12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T10:V12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U10:W12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U10:W12,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V10:X12,$AK$9:$AM$11)/$AK$13</f>
-        <v>-63.75</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V10:X12,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="BC74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W10:Y12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W10:Y12,$AK$9:$AM$11)/$AK$13))</f>
         <v>63.75</v>
       </c>
       <c r="BD74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X10:Z12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X10:Z12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y10:AA12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y10:AA12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z10:AB12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z10:AB12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA10:AC12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA10:AC12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB10:AD12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB10:AD12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI74" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC10:AE12,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC10:AE12,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -12919,115 +12919,115 @@
         <v>0</v>
       </c>
       <c r="AH75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B11:D13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B11:D13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C11:E13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C11:E13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D11:F13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D11:F13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E11:G13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E11:G13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F11:H13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F11:H13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G11:I13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G11:I13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H11:J13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H11:J13,$AK$9:$AM$11)/$AK$13))</f>
         <v>95.625</v>
       </c>
       <c r="AO75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I11:K13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I11:K13,$AK$9:$AM$11)/$AK$13))</f>
         <v>111.5625</v>
       </c>
       <c r="AP75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J11:L13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J11:L13,$AK$9:$AM$11)/$AK$13))</f>
         <v>63.75</v>
       </c>
       <c r="AQ75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K11:M13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K11:M13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AR75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L11:N13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L11:N13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M11:O13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M11:O13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N11:P13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N11:P13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O11:Q13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O11:Q13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P11:R13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P11:R13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q11:S13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q11:S13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R11:T13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R11:T13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S11:U13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S11:U13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T11:V13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T11:V13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U11:W13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U11:W13,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V11:X13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V11:X13,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="BC75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W11:Y13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W11:Y13,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BD75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X11:Z13,$AK$9:$AM$11)/$AK$13</f>
-        <v>-47.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X11:Z13,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="BE75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y11:AA13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y11:AA13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z11:AB13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z11:AB13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA11:AC13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA11:AC13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB11:AD13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB11:AD13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI75" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC11:AE13,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC11:AE13,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -13145,115 +13145,115 @@
         <v>0</v>
       </c>
       <c r="AH76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B12:D14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B12:D14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C12:E14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C12:E14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D12:F14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D12:F14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E12:G14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E12:G14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F12:H14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F12:H14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G12:I14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G12:I14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H12:J14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H12:J14,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AO76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I12:K14,$AK$9:$AM$11)/$AK$13</f>
-        <v>-31.875</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I12:K14,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="AP76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J12:L14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J12:L14,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AQ76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K12:M14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K12:M14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AR76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L12:N14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L12:N14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M12:O14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M12:O14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N12:P14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N12:P14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O12:Q14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O12:Q14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P12:R14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P12:R14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q12:S14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q12:S14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R12:T14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R12:T14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S12:U14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S12:U14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T12:V14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T12:V14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U12:W14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U12:W14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V12:X14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V12:X14,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BC76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W12:Y14,$AK$9:$AM$11)/$AK$13</f>
-        <v>-63.75</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W12:Y14,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="BD76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X12:Z14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X12:Z14,$AK$9:$AM$11)/$AK$13))</f>
         <v>63.75</v>
       </c>
       <c r="BE76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y12:AA14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y12:AA14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z12:AB14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z12:AB14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA12:AC14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA12:AC14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB12:AD14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB12:AD14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI76" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC12:AE14,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC12:AE14,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -13371,115 +13371,115 @@
         <v>0</v>
       </c>
       <c r="AH77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B13:D15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B13:D15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C13:E15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C13:E15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D13:F15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D13:F15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E13:G15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E13:G15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F13:H15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F13:H15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G13:I15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G13:I15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H13:J15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H13:J15,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AO77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I13:K15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I13:K15,$AK$9:$AM$11)/$AK$13))</f>
         <v>111.5625</v>
       </c>
       <c r="AP77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J13:L15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J13:L15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AQ77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K13:M15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K13:M15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AR77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L13:N15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L13:N15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M13:O15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M13:O15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N13:P15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N13:P15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O13:Q15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O13:Q15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P13:R15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P13:R15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q13:S15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q13:S15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R13:T15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R13:T15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S13:U15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S13:U15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T13:V15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T13:V15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U13:W15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U13:W15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V13:X15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V13:X15,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BC77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W13:Y15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W13:Y15,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BD77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X13:Z15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X13:Z15,$AK$9:$AM$11)/$AK$13))</f>
         <v>143.4375</v>
       </c>
       <c r="BE77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y13:AA15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y13:AA15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z13:AB15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z13:AB15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA13:AC15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA13:AC15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB13:AD15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB13:AD15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI77" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC13:AE15,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC13:AE15,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -13597,115 +13597,115 @@
         <v>0</v>
       </c>
       <c r="AH78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B14:D16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B14:D16,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C14:E16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C14:E16,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D14:F16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D14:F16,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E14:G16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E14:G16,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F14:H16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F14:H16,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G14:I16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G14:I16,$AK$9:$AM$11)/$AK$13))</f>
         <v>95.625</v>
       </c>
       <c r="AN78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H14:J16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H14:J16,$AK$9:$AM$11)/$AK$13))</f>
         <v>111.5625</v>
       </c>
       <c r="AO78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I14:K16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I14:K16,$AK$9:$AM$11)/$AK$13))</f>
         <v>63.75</v>
       </c>
       <c r="AP78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J14:L16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J14:L16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AQ78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K14:M16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K14:M16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AR78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L14:N16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L14:N16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M14:O16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M14:O16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N14:P16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N14:P16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O14:Q16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O14:Q16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P14:R16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P14:R16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q14:S16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q14:S16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R14:T16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R14:T16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S14:U16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S14:U16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T14:V16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T14:V16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U14:W16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U14:W16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V14:X16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V14:X16,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BC78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W14:Y16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W14:Y16,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="BD78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X14:Z16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X14:Z16,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BE78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y14:AA16,$AK$9:$AM$11)/$AK$13</f>
-        <v>-47.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y14:AA16,$AK$9:$AM$11)/$AK$13))</f>
+        <v>0</v>
       </c>
       <c r="BF78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z14:AB16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z14:AB16,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA14:AC16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA14:AC16,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB14:AD16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB14:AD16,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI78" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC14:AE16,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC14:AE16,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -13823,115 +13823,115 @@
         <v>0</v>
       </c>
       <c r="AH79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B15:D17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B15:D17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C15:E17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C15:E17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D15:F17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D15:F17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E15:G17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E15:G17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F15:H17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F15:H17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G15:I17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G15:I17,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="AN79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H15:J17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H15:J17,$AK$9:$AM$11)/$AK$13))</f>
         <v>31.875</v>
       </c>
       <c r="AO79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I15:K17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I15:K17,$AK$9:$AM$11)/$AK$13))</f>
         <v>223.125</v>
       </c>
       <c r="AP79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J15:L17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J15:L17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AQ79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K15:M17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K15:M17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AR79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L15:N17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L15:N17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M15:O17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M15:O17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N15:P17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N15:P17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O15:Q17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O15:Q17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P15:R17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P15:R17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q15:S17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q15:S17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R15:T17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R15:T17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S15:U17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S15:U17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T15:V17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T15:V17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U15:W17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U15:W17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V15:X17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V15:X17,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BC79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W15:Y17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W15:Y17,$AK$9:$AM$11)/$AK$13))</f>
         <v>159.375</v>
       </c>
       <c r="BD79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X15:Z17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X15:Z17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y15:AA17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y15:AA17,$AK$9:$AM$11)/$AK$13))</f>
         <v>111.5625</v>
       </c>
       <c r="BF79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z15:AB17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z15:AB17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA15:AC17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA15:AC17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB15:AD17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB15:AD17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI79" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC15:AE17,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC15:AE17,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -14049,115 +14049,115 @@
         <v>0</v>
       </c>
       <c r="AH80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B16:D18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B16:D18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C16:E18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C16:E18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D16:F18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D16:F18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E16:G18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E16:G18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F16:H18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F16:H18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G16:I18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G16:I18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H16:J18,$AK$9:$AM$11)/$AK$13</f>
-        <v>318.75</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H16:J18,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AO80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I16:K18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I16:K18,$AK$9:$AM$11)/$AK$13))</f>
         <v>191.25</v>
       </c>
       <c r="AP80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J16:L18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J16:L18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AQ80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K16:M18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K16:M18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AR80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L16:N18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L16:N18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M16:O18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M16:O18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N16:P18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N16:P18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O16:Q18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O16:Q18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P16:R18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P16:R18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q16:S18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q16:S18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R16:T18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R16:T18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S16:U18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S16:U18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T16:V18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T16:V18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U16:W18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U16:W18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V16:X18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V16:X18,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BC80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W16:Y18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W16:Y18,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BD80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X16:Z18,$AK$9:$AM$11)/$AK$13</f>
-        <v>286.875</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X16:Z18,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="BE80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y16:AA18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y16:AA18,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BF80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z16:AB18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z16:AB18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA16:AC18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA16:AC18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB16:AD18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB16:AD18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI80" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC16:AE18,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC16:AE18,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -14275,115 +14275,115 @@
         <v>0</v>
       </c>
       <c r="AH81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B17:D19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B17:D19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C17:E19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C17:E19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D17:F19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D17:F19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E17:G19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E17:G19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F17:H19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F17:H19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G17:I19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G17:I19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H17:J19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H17:J19,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AO81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I17:K19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I17:K19,$AK$9:$AM$11)/$AK$13))</f>
         <v>111.5625</v>
       </c>
       <c r="AP81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J17:L19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J17:L19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AQ81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K17:M19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K17:M19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AR81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L17:N19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L17:N19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M17:O19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M17:O19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N17:P19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N17:P19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O17:Q19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O17:Q19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P17:R19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P17:R19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q17:S19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q17:S19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R17:T19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R17:T19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S17:U19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S17:U19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T17:V19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T17:V19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U17:W19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U17:W19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V17:X19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V17:X19,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BC81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W17:Y19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W17:Y19,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BD81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X17:Z19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X17:Z19,$AK$9:$AM$11)/$AK$13))</f>
         <v>143.4375</v>
       </c>
       <c r="BE81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y17:AA19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y17:AA19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z17:AB19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z17:AB19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA17:AC19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA17:AC19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB17:AD19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB17:AD19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI81" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC17:AE19,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC17:AE19,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -14501,115 +14501,115 @@
         <v>0</v>
       </c>
       <c r="AH82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B18:D20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B18:D20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C18:E20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C18:E20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D18:F20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D18:F20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E18:G20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E18:G20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F18:H20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F18:H20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G18:I20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G18:I20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H18:J20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H18:J20,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="AO82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I18:K20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I18:K20,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AP82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J18:L20,$AK$9:$AM$11)/$AK$13</f>
-        <v>302.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J18:L20,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AQ82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K18:M20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K18:M20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AR82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L18:N20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L18:N20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M18:O20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M18:O20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N18:P20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N18:P20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O18:Q20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O18:Q20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P18:R20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P18:R20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q18:S20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q18:S20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R18:T20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R18:T20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S18:U20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S18:U20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T18:V20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T18:V20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U18:W20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U18:W20,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V18:X20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V18:X20,$AK$9:$AM$11)/$AK$13))</f>
         <v>159.375</v>
       </c>
       <c r="BC82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W18:Y20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W18:Y20,$AK$9:$AM$11)/$AK$13))</f>
         <v>143.4375</v>
       </c>
       <c r="BD82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X18:Z20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X18:Z20,$AK$9:$AM$11)/$AK$13))</f>
         <v>191.25</v>
       </c>
       <c r="BE82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y18:AA20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y18:AA20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z18:AB20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z18:AB20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA18:AC20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA18:AC20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB18:AD20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB18:AD20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI82" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC18:AE20,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC18:AE20,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -14727,115 +14727,115 @@
         <v>0</v>
       </c>
       <c r="AH83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B19:D21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B19:D21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C19:E21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C19:E21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D19:F21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D19:F21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E19:G21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E19:G21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F19:H21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F19:H21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G19:I21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G19:I21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H19:J21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H19:J21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I19:K21,$AK$9:$AM$11)/$AK$13</f>
-        <v>318.75</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I19:K21,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AP83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J19:L21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J19:L21,$AK$9:$AM$11)/$AK$13))</f>
         <v>191.25</v>
       </c>
       <c r="AQ83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K19:M21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K19:M21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AR83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L19:N21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L19:N21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M19:O21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M19:O21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N19:P21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N19:P21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O19:Q21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O19:Q21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P19:R21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P19:R21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q19:S21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q19:S21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R19:T21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R19:T21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S19:U21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S19:U21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T19:V21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T19:V21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U19:W21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U19:W21,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BB83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V19:X21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V19:X21,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BC83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W19:Y21,$AK$9:$AM$11)/$AK$13</f>
-        <v>286.875</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W19:Y21,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="BD83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X19:Z21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X19:Z21,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BE83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y19:AA21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y19:AA21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z19:AB21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z19:AB21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA19:AC21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA19:AC21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB19:AD21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB19:AD21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI83" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC19:AE21,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC19:AE21,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -14953,115 +14953,115 @@
         <v>0</v>
       </c>
       <c r="AH84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B20:D22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B20:D22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C20:E22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C20:E22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D20:F22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D20:F22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E20:G22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E20:G22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F20:H22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F20:H22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G20:I22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G20:I22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H20:J22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H20:J22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I20:K22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I20:K22,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="AP84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J20:L22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J20:L22,$AK$9:$AM$11)/$AK$13))</f>
         <v>175.3125</v>
       </c>
       <c r="AQ84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K20:M22,$AK$9:$AM$11)/$AK$13</f>
-        <v>302.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K20:M22,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AR84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L20:N22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L20:N22,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AS84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M20:O22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M20:O22,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AT84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N20:P22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N20:P22,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O20:Q22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O20:Q22,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P20:R22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P20:R22,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q20:S22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q20:S22,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R20:T22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R20:T22,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S20:U22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S20:U22,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AZ84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T20:V22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T20:V22,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="BA84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U20:W22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U20:W22,$AK$9:$AM$11)/$AK$13))</f>
         <v>159.375</v>
       </c>
       <c r="BB84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V20:X22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V20:X22,$AK$9:$AM$11)/$AK$13))</f>
         <v>143.4375</v>
       </c>
       <c r="BC84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W20:Y22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W20:Y22,$AK$9:$AM$11)/$AK$13))</f>
         <v>191.25</v>
       </c>
       <c r="BD84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X20:Z22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X20:Z22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y20:AA22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y20:AA22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z20:AB22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z20:AB22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA20:AC22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA20:AC22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB20:AD22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB20:AD22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI84" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC20:AE22,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC20:AE22,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -15179,115 +15179,115 @@
         <v>0</v>
       </c>
       <c r="AH85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B21:D23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B21:D23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C21:E23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C21:E23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D21:F23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D21:F23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E21:G23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E21:G23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F21:H23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F21:H23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G21:I23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G21:I23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H21:J23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H21:J23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I21:K23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I21:K23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J21:L23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J21:L23,$AK$9:$AM$11)/$AK$13))</f>
         <v>223.125</v>
       </c>
       <c r="AQ85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K21:M23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K21:M23,$AK$9:$AM$11)/$AK$13))</f>
         <v>159.375</v>
       </c>
       <c r="AR85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L21:N23,$AK$9:$AM$11)/$AK$13</f>
-        <v>366.5625</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L21:N23,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AS85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M21:O23,$AK$9:$AM$11)/$AK$13</f>
-        <v>302.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M21:O23,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AT85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N21:P23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N21:P23,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AU85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O21:Q23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O21:Q23,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AV85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P21:R23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P21:R23,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AW85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q21:S23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q21:S23,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AX85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R21:T23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R21:T23,$AK$9:$AM$11)/$AK$13))</f>
         <v>255</v>
       </c>
       <c r="AY85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S21:U23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S21:U23,$AK$9:$AM$11)/$AK$13))</f>
         <v>159.375</v>
       </c>
       <c r="AZ85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T21:V23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T21:V23,$AK$9:$AM$11)/$AK$13))</f>
         <v>223.125</v>
       </c>
       <c r="BA85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U21:W23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U21:W23,$AK$9:$AM$11)/$AK$13))</f>
         <v>191.25</v>
       </c>
       <c r="BB85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V21:X23,$AK$9:$AM$11)/$AK$13</f>
-        <v>334.6875</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V21:X23,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="BC85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W21:Y23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W21:Y23,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BD85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X21:Z23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X21:Z23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y21:AA23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y21:AA23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z21:AB23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z21:AB23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA21:AC23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA21:AC23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB21:AD23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB21:AD23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI85" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC21:AE23,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC21:AE23,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -15405,115 +15405,115 @@
         <v>0</v>
       </c>
       <c r="AH86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B22:D24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B22:D24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C22:E24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C22:E24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D22:F24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D22:F24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E22:G24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E22:G24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F22:H24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F22:H24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G22:I24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G22:I24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H22:J24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H22:J24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I22:K24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I22:K24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J22:L24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J22:L24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K22:M24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K22:M24,$AK$9:$AM$11)/$AK$13))</f>
         <v>143.4375</v>
       </c>
       <c r="AR86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L22:N24,$AK$9:$AM$11)/$AK$13</f>
-        <v>302.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L22:N24,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AS86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M22:O24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M22:O24,$AK$9:$AM$11)/$AK$13))</f>
         <v>159.375</v>
       </c>
       <c r="AT86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N22:P24,$AK$9:$AM$11)/$AK$13</f>
-        <v>270.9375</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N22:P24,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AU86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O22:Q24,$AK$9:$AM$11)/$AK$13</f>
-        <v>366.5625</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O22:Q24,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AV86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P22:R24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P22:R24,$AK$9:$AM$11)/$AK$13))</f>
         <v>207.1875</v>
       </c>
       <c r="AW86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q22:S24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q22:S24,$AK$9:$AM$11)/$AK$13))</f>
         <v>223.125</v>
       </c>
       <c r="AX86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R22:T24,$AK$9:$AM$11)/$AK$13</f>
-        <v>270.9375</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R22:T24,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AY86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S22:U24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S22:U24,$AK$9:$AM$11)/$AK$13))</f>
         <v>191.25</v>
       </c>
       <c r="AZ86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T22:V24,$AK$9:$AM$11)/$AK$13</f>
-        <v>334.6875</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T22:V24,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="BA86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U22:W24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U22:W24,$AK$9:$AM$11)/$AK$13))</f>
         <v>223.125</v>
       </c>
       <c r="BB86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V22:X24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V22:X24,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BC86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W22:Y24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W22:Y24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X22:Z24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X22:Z24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y22:AA24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y22:AA24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z22:AB24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z22:AB24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA22:AC24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA22:AC24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB22:AD24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB22:AD24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI86" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC22:AE24,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC22:AE24,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -15631,115 +15631,115 @@
         <v>0</v>
       </c>
       <c r="AH87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B23:D25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B23:D25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C23:E25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C23:E25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D23:F25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D23:F25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E23:G25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E23:G25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F23:H25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F23:H25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G23:I25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G23:I25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H23:J25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H23:J25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I23:K25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I23:K25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J23:L25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J23:L25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K23:M25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K23:M25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L23:N25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L23:N25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M23:O25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M23:O25,$AK$9:$AM$11)/$AK$13))</f>
         <v>143.4375</v>
       </c>
       <c r="AT87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N23:P25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N23:P25,$AK$9:$AM$11)/$AK$13))</f>
         <v>223.125</v>
       </c>
       <c r="AU87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O23:Q25,$AK$9:$AM$11)/$AK$13</f>
-        <v>302.8125</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O23:Q25,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AV87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P23:R25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P23:R25,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="AW87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q23:S25,$AK$9:$AM$11)/$AK$13</f>
-        <v>334.6875</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q23:S25,$AK$9:$AM$11)/$AK$13))</f>
+        <v>255</v>
       </c>
       <c r="AX87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R23:T25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R23:T25,$AK$9:$AM$11)/$AK$13))</f>
         <v>223.125</v>
       </c>
       <c r="AY87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S23:U25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S23:U25,$AK$9:$AM$11)/$AK$13))</f>
         <v>223.125</v>
       </c>
       <c r="AZ87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T23:V25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T23:V25,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="BA87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U23:W25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U23:W25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V23:X25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V23:X25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W23:Y25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W23:Y25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X23:Z25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X23:Z25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y23:AA25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y23:AA25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z23:AB25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z23:AB25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA23:AC25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA23:AC25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB23:AD25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB23:AD25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI87" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC23:AE25,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC23:AE25,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -15857,115 +15857,115 @@
         <v>0</v>
       </c>
       <c r="AH88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B24:D26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B24:D26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C24:E26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C24:E26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D24:F26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D24:F26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E24:G26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E24:G26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F24:H26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F24:H26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G24:I26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G24:I26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H24:J26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H24:J26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I24:K26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I24:K26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J24:L26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J24:L26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K24:M26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K24:M26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L24:N26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L24:N26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M24:O26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M24:O26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N24:P26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N24:P26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O24:Q26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O24:Q26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P24:R26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P24:R26,$AK$9:$AM$11)/$AK$13))</f>
         <v>143.4375</v>
       </c>
       <c r="AW88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q24:S26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q24:S26,$AK$9:$AM$11)/$AK$13))</f>
         <v>79.6875</v>
       </c>
       <c r="AX88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R24:T26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R24:T26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S24:U26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S24:U26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T24:V26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T24:V26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U24:W26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U24:W26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V24:X26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V24:X26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W24:Y26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W24:Y26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X24:Z26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X24:Z26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y24:AA26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y24:AA26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z24:AB26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z24:AB26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA24:AC26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA24:AC26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB24:AD26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB24:AD26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI88" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC24:AE26,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC24:AE26,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -16083,115 +16083,115 @@
         <v>0</v>
       </c>
       <c r="AH89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B25:D27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B25:D27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C25:E27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C25:E27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D25:F27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D25:F27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E25:G27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E25:G27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F25:H27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F25:H27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G25:I27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G25:I27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H25:J27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H25:J27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I25:K27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I25:K27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J25:L27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J25:L27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K25:M27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K25:M27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L25:N27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L25:N27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M25:O27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M25:O27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N25:P27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N25:P27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O25:Q27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O25:Q27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P25:R27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P25:R27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AW89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q25:S27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q25:S27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AX89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R25:T27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R25:T27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S25:U27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S25:U27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T25:V27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T25:V27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U25:W27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U25:W27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V25:X27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V25:X27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W25:Y27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W25:Y27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X25:Z27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X25:Z27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y25:AA27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y25:AA27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z25:AB27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z25:AB27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA25:AC27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA25:AC27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB25:AD27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB25:AD27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI89" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC25:AE27,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC25:AE27,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -16309,115 +16309,115 @@
         <v>0</v>
       </c>
       <c r="AH90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B26:D28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B26:D28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C26:E28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C26:E28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D26:F28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D26:F28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E26:G28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E26:G28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F26:H28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F26:H28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G26:I28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G26:I28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H26:J28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H26:J28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I26:K28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I26:K28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J26:L28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J26:L28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K26:M28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K26:M28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L26:N28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L26:N28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M26:O28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M26:O28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N26:P28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N26:P28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O26:Q28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O26:Q28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P26:R28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P26:R28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AW90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q26:S28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q26:S28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AX90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R26:T28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R26:T28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S26:U28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S26:U28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T26:V28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T26:V28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U26:W28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U26:W28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V26:X28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V26:X28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W26:Y28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W26:Y28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X26:Z28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X26:Z28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y26:AA28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y26:AA28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z26:AB28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z26:AB28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA26:AC28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA26:AC28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB26:AD28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB26:AD28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI90" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC26:AE28,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC26:AE28,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -16535,115 +16535,115 @@
         <v>0</v>
       </c>
       <c r="AH91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B27:D29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B27:D29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C27:E29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C27:E29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D27:F29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D27:F29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E27:G29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E27:G29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F27:H29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F27:H29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G27:I29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G27:I29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H27:J29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H27:J29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I27:K29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I27:K29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J27:L29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J27:L29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K27:M29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K27:M29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L27:N29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L27:N29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M27:O29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M27:O29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N27:P29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N27:P29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O27:Q29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O27:Q29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P27:R29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P27:R29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AW91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q27:S29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q27:S29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AX91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R27:T29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R27:T29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S27:U29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S27:U29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T27:V29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T27:V29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U27:W29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U27:W29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V27:X29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V27:X29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W27:Y29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W27:Y29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X27:Z29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X27:Z29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y27:AA29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y27:AA29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z27:AB29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z27:AB29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA27:AC29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA27:AC29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB27:AD29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB27:AD29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI91" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC27:AE29,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC27:AE29,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -16761,229 +16761,229 @@
         <v>0</v>
       </c>
       <c r="AH92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B28:D30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B28:D30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C28:E30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C28:E30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D28:F30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D28:F30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E28:G30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E28:G30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F28:H30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F28:H30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G28:I30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G28:I30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H28:J30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H28:J30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I28:K30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I28:K30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J28:L30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J28:L30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K28:M30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K28:M30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L28:N30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L28:N30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M28:O30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M28:O30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N28:P30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N28:P30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O28:Q30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O28:Q30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P28:R30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P28:R30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AW92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q28:S30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q28:S30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AX92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R28:T30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R28:T30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S28:U30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S28:U30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T28:V30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T28:V30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U28:W30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U28:W30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V28:X30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V28:X30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W28:Y30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W28:Y30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X28:Z30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X28:Z30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y28:AA30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y28:AA30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z28:AB30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z28:AB30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA28:AC30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA28:AC30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB28:AD30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB28:AD30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI92" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC28:AE30,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC28:AE30,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="AH93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B29:D31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B29:D31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AI93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C29:E31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C29:E31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AJ93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D29:F31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D29:F31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AK93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E29:G31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E29:G31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AL93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F29:H31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F29:H31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AM93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G29:I31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G29:I31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AN93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H29:J31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H29:J31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AO93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I29:K31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I29:K31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AP93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J29:L31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J29:L31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AQ93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K29:M31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K29:M31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AR93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L29:N31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L29:N31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AS93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M29:O31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M29:O31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AT93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N29:P31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N29:P31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AU93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O29:Q31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O29:Q31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AV93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P29:R31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P29:R31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AW93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q29:S31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q29:S31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AX93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R29:T31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R29:T31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AY93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S29:U31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S29:U31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="AZ93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T29:V31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T29:V31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BA93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U29:W31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U29:W31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BB93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V29:X31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V29:X31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BC93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W29:Y31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W29:Y31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BD93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X29:Z31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X29:Z31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BE93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y29:AA31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y29:AA31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BF93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z29:AB31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z29:AB31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BG93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA29:AC31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA29:AC31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BH93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB29:AD31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB29:AD31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
       <c r="BI93" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC29:AE31,$AK$9:$AM$11)/$AK$13</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC29:AE31,$AK$9:$AM$11)/$AK$13))</f>
         <v>0</v>
       </c>
     </row>
@@ -17112,115 +17112,115 @@
         <v>0</v>
       </c>
       <c r="AH96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B2:D4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B2:D4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C2:E4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C2:E4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D2:F4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D2:F4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E2:G4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E2:G4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F2:H4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F2:H4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G2:I4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G2:I4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H2:J4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H2:J4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I2:K4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I2:K4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J2:L4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J2:L4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K2:M4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K2:M4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L2:N4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L2:N4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M2:O4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M2:O4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N2:P4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N2:P4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O2:Q4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O2:Q4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AV96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P2:R4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P2:R4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AW96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q2:S4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q2:S4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AX96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R2:T4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R2:T4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S2:U4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S2:U4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T2:V4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T2:V4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U2:W4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U2:W4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V2:X4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V2:X4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W2:Y4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W2:Y4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X2:Z4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X2:Z4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y2:AA4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y2:AA4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z2:AB4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z2:AB4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA2:AC4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA2:AC4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB2:AD4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB2:AD4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI96" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC2:AE4,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC2:AE4,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -17338,115 +17338,115 @@
         <v>0</v>
       </c>
       <c r="AH97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B3:D5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B3:D5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C3:E5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C3:E5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D3:F5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D3:F5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E3:G5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E3:G5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F3:H5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F3:H5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G3:I5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G3:I5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H3:J5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H3:J5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I3:K5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I3:K5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J3:L5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J3:L5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K3:M5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K3:M5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L3:N5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L3:N5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M3:O5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M3:O5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N3:P5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N3:P5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O3:Q5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O3:Q5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AV97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P3:R5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P3:R5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AW97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q3:S5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q3:S5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AX97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R3:T5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R3:T5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S3:U5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S3:U5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T3:V5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T3:V5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U3:W5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U3:W5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V3:X5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V3:X5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W3:Y5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W3:Y5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X3:Z5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X3:Z5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y3:AA5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y3:AA5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z3:AB5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z3:AB5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA3:AC5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA3:AC5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB3:AD5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB3:AD5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI97" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC3:AE5,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC3:AE5,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -17564,115 +17564,115 @@
         <v>0</v>
       </c>
       <c r="AH98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B4:D6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B4:D6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C4:E6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C4:E6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D4:F6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D4:F6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E4:G6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E4:G6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F4:H6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F4:H6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G4:I6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G4:I6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H4:J6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H4:J6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I4:K6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I4:K6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J4:L6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J4:L6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K4:M6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K4:M6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L4:N6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L4:N6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M4:O6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M4:O6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N4:P6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N4:P6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O4:Q6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O4:Q6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AV98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P4:R6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P4:R6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AW98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q4:S6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q4:S6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AX98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R4:T6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R4:T6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S4:U6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S4:U6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T4:V6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T4:V6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U4:W6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U4:W6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V4:X6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V4:X6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W4:Y6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W4:Y6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X4:Z6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X4:Z6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y4:AA6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y4:AA6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z4:AB6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z4:AB6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA4:AC6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA4:AC6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB4:AD6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB4:AD6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI98" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC4:AE6,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC4:AE6,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -17790,115 +17790,115 @@
         <v>0</v>
       </c>
       <c r="AH99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B5:D7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B5:D7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C5:E7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C5:E7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D5:F7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D5:F7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E5:G7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E5:G7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F5:H7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F5:H7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G5:I7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G5:I7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H5:J7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H5:J7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I5:K7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I5:K7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J5:L7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J5:L7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K5:M7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K5:M7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L5:N7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L5:N7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M5:O7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M5:O7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N5:P7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N5:P7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O5:Q7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O5:Q7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AV99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P5:R7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P5:R7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AW99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q5:S7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q5:S7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AX99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R5:T7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R5:T7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S5:U7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S5:U7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T5:V7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T5:V7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U5:W7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U5:W7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V5:X7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V5:X7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W5:Y7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W5:Y7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X5:Z7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X5:Z7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y5:AA7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y5:AA7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z5:AB7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z5:AB7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA5:AC7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA5:AC7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB5:AD7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB5:AD7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI99" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC5:AE7,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC5:AE7,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -18016,115 +18016,115 @@
         <v>0</v>
       </c>
       <c r="AH100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B6:D8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B6:D8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C6:E8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C6:E8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D6:F8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D6:F8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E6:G8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E6:G8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F6:H8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F6:H8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G6:I8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G6:I8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H6:J8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H6:J8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I6:K8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I6:K8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J6:L8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J6:L8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K6:M8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K6:M8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L6:N8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L6:N8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M6:O8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M6:O8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N6:P8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N6:P8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O6:Q8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O6:Q8,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AV100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P6:R8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P6:R8,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AW100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q6:S8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q6:S8,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AX100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R6:T8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R6:T8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S6:U8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S6:U8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T6:V8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T6:V8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U6:W8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U6:W8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V6:X8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V6:X8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W6:Y8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W6:Y8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X6:Z8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X6:Z8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y6:AA8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y6:AA8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z6:AB8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z6:AB8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA6:AC8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA6:AC8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB6:AD8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB6:AD8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI100" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC6:AE8,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC6:AE8,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -18242,115 +18242,115 @@
         <v>0</v>
       </c>
       <c r="AH101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B7:D9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B7:D9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C7:E9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C7:E9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D7:F9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D7:F9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK101" s="13" t="e">
-        <f aca="false">SUMPRODUCT(E7:G9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E7:G9,$AK$16:$AM$18)/$AK$20))</f>
         <v>#NAME?</v>
       </c>
       <c r="AL101" s="13" t="e">
-        <f aca="false">SUMPRODUCT(F7:H9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F7:H9,$AK$16:$AM$18)/$AK$20))</f>
         <v>#NAME?</v>
       </c>
       <c r="AM101" s="13" t="e">
-        <f aca="false">SUMPRODUCT(G7:I9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G7:I9,$AK$16:$AM$18)/$AK$20))</f>
         <v>#NAME?</v>
       </c>
       <c r="AN101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H7:J9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H7:J9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I7:K9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I7:K9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J7:L9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J7:L9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K7:M9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K7:M9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L7:N9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L7:N9,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AS101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M7:O9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M7:O9,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="AT101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N7:P9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N7:P9,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="AU101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O7:Q9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O7:Q9,$AK$16:$AM$18)/$AK$20))</f>
         <v>113.333333333333</v>
       </c>
       <c r="AV101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P7:R9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P7:R9,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AW101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q7:S9,$AK$16:$AM$18)/$AK$20</f>
-        <v>340</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q7:S9,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AX101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R7:T9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R7:T9,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="AY101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S7:U9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S7:U9,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="AZ101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T7:V9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T7:V9,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="BA101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U7:W9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U7:W9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V7:X9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V7:X9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W7:Y9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W7:Y9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X7:Z9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X7:Z9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y7:AA9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y7:AA9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z7:AB9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z7:AB9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA7:AC9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA7:AC9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB7:AD9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB7:AD9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI101" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC7:AE9,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC7:AE9,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -18468,115 +18468,115 @@
         <v>0</v>
       </c>
       <c r="AH102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B8:D10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B8:D10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C8:E10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C8:E10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D8:F10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D8:F10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK102" s="13" t="e">
-        <f aca="false">SUMPRODUCT(E8:G10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E8:G10,$AK$16:$AM$18)/$AK$20))</f>
         <v>#NAME?</v>
       </c>
       <c r="AL102" s="13" t="e">
-        <f aca="false">SUMPRODUCT(F8:H10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F8:H10,$AK$16:$AM$18)/$AK$20))</f>
         <v>#NAME?</v>
       </c>
       <c r="AM102" s="13" t="e">
-        <f aca="false">SUMPRODUCT(G8:I10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G8:I10,$AK$16:$AM$18)/$AK$20))</f>
         <v>#NAME?</v>
       </c>
       <c r="AN102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H8:J10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H8:J10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I8:K10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I8:K10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J8:L10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J8:L10,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AQ102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K8:M10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K8:M10,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="AR102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L8:N10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L8:N10,$AK$16:$AM$18)/$AK$20))</f>
         <v>113.333333333333</v>
       </c>
       <c r="AS102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M8:O10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M8:O10,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="AT102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N8:P10,$AK$16:$AM$18)/$AK$20</f>
-        <v>425</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N8:P10,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AU102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O8:Q10,$AK$16:$AM$18)/$AK$20</f>
-        <v>566.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O8:Q10,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AV102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P8:R10,$AK$16:$AM$18)/$AK$20</f>
-        <v>311.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P8:R10,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AW102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q8:S10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q8:S10,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="AX102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R8:T10,$AK$16:$AM$18)/$AK$20</f>
-        <v>425</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R8:T10,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AY102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S8:U10,$AK$16:$AM$18)/$AK$20</f>
-        <v>396.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S8:U10,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AZ102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T8:V10,$AK$16:$AM$18)/$AK$20</f>
-        <v>340</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T8:V10,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="BA102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U8:W10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U8:W10,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="BB102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V8:X10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V8:X10,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="BC102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W8:Y10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W8:Y10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X8:Z10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X8:Z10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y8:AA10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y8:AA10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z8:AB10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z8:AB10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA8:AC10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA8:AC10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB8:AD10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB8:AD10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI102" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC8:AE10,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC8:AE10,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -18694,115 +18694,115 @@
         <v>0</v>
       </c>
       <c r="AH103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B9:D11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B9:D11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C9:E11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C9:E11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D9:F11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D9:F11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK103" s="13" t="e">
-        <f aca="false">SUMPRODUCT(E9:G11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E9:G11,$AK$16:$AM$18)/$AK$20))</f>
         <v>#NAME?</v>
       </c>
       <c r="AL103" s="13" t="e">
-        <f aca="false">SUMPRODUCT(F9:H11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F9:H11,$AK$16:$AM$18)/$AK$20))</f>
         <v>#NAME?</v>
       </c>
       <c r="AM103" s="13" t="e">
-        <f aca="false">SUMPRODUCT(G9:I11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G9:I11,$AK$16:$AM$18)/$AK$20))</f>
         <v>#NAME?</v>
       </c>
       <c r="AN103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H9:J11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H9:J11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I9:K11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I9:K11,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AP103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J9:L11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J9:L11,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="AQ103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K9:M11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K9:M11,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="AR103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L9:N11,$AK$16:$AM$18)/$AK$20</f>
-        <v>566.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L9:N11,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AS103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M9:O11,$AK$16:$AM$18)/$AK$20</f>
-        <v>453.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M9:O11,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AT103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N9:P11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N9:P11,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O9:Q11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O9:Q11,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P9:R11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P9:R11,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q9:S11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q9:S11,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R9:T11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R9:T11,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S9:U11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S9:U11,$AK$16:$AM$18)/$AK$20))</f>
         <v>113.333333333333</v>
       </c>
       <c r="AZ103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T9:V11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T9:V11,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="BA103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U9:W11,$AK$16:$AM$18)/$AK$20</f>
-        <v>396.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U9:W11,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="BB103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V9:X11,$AK$16:$AM$18)/$AK$20</f>
-        <v>311.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V9:X11,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="BC103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W9:Y11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W9:Y11,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="BD103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X9:Z11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X9:Z11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y9:AA11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y9:AA11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z9:AB11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z9:AB11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA9:AC11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA9:AC11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB9:AD11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB9:AD11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI103" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC9:AE11,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC9:AE11,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -18920,115 +18920,115 @@
         <v>0</v>
       </c>
       <c r="AH104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B10:D12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B10:D12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C10:E12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C10:E12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D10:F12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D10:F12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E10:G12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E10:G12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F10:H12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F10:H12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G10:I12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G10:I12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H10:J12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H10:J12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I10:K12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I10:K12,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="AP104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J10:L12,$AK$16:$AM$18)/$AK$20</f>
-        <v>283.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J10:L12,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AQ104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K10:M12,$AK$16:$AM$18)/$AK$20</f>
-        <v>453.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K10:M12,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AR104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L10:N12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L10:N12,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M10:O12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M10:O12,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N10:P12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N10:P12,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O10:Q12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O10:Q12,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P10:R12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P10:R12,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q10:S12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q10:S12,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R10:T12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R10:T12,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S10:U12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S10:U12,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T10:V12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T10:V12,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U10:W12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U10:W12,$AK$16:$AM$18)/$AK$20))</f>
         <v>113.333333333333</v>
       </c>
       <c r="BB104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V10:X12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V10:X12,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="BC104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W10:Y12,$AK$16:$AM$18)/$AK$20</f>
-        <v>283.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W10:Y12,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="BD104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X10:Z12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X10:Z12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y10:AA12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y10:AA12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z10:AB12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z10:AB12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA10:AC12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA10:AC12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB10:AD12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB10:AD12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI104" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC10:AE12,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC10:AE12,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -19146,115 +19146,115 @@
         <v>0</v>
       </c>
       <c r="AH105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B11:D13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B11:D13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C11:E13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C11:E13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D11:F13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D11:F13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E11:G13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E11:G13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F11:H13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F11:H13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G11:I13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G11:I13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H11:J13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H11:J13,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AO105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I11:K13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I11:K13,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="AP105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J11:L13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J11:L13,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="AQ105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K11:M13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K11:M13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AR105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L11:N13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L11:N13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M11:O13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M11:O13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N11:P13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N11:P13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O11:Q13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O11:Q13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P11:R13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P11:R13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q11:S13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q11:S13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R11:T13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R11:T13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S11:U13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S11:U13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T11:V13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T11:V13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U11:W13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U11:W13,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BB105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V11:X13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V11:X13,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="BC105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W11:Y13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W11:Y13,$AK$16:$AM$18)/$AK$20))</f>
         <v>113.333333333333</v>
       </c>
       <c r="BD105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X11:Z13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X11:Z13,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="BE105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y11:AA13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y11:AA13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z11:AB13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z11:AB13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA11:AC13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA11:AC13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB11:AD13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB11:AD13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI105" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC11:AE13,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC11:AE13,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -19372,115 +19372,115 @@
         <v>0</v>
       </c>
       <c r="AH106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B12:D14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B12:D14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C12:E14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C12:E14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D12:F14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D12:F14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E12:G14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E12:G14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F12:H14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F12:H14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G12:I14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G12:I14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H12:J14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H12:J14,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="AO106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I12:K14,$AK$16:$AM$18)/$AK$20</f>
-        <v>283.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I12:K14,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AP106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J12:L14,$AK$16:$AM$18)/$AK$20</f>
-        <v>453.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J12:L14,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AQ106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K12:M14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K12:M14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AR106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L12:N14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L12:N14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M12:O14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M12:O14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N12:P14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N12:P14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O12:Q14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O12:Q14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P12:R14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P12:R14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q12:S14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q12:S14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R12:T14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R12:T14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S12:U14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S12:U14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T12:V14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T12:V14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U12:W14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U12:W14,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BB106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V12:X14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V12:X14,$AK$16:$AM$18)/$AK$20))</f>
         <v>113.333333333333</v>
       </c>
       <c r="BC106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W12:Y14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W12:Y14,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="BD106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X12:Z14,$AK$16:$AM$18)/$AK$20</f>
-        <v>283.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X12:Z14,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="BE106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y12:AA14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y12:AA14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z12:AB14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z12:AB14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA12:AC14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA12:AC14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB12:AD14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB12:AD14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI106" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC12:AE14,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC12:AE14,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -19598,115 +19598,115 @@
         <v>0</v>
       </c>
       <c r="AH107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B13:D15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B13:D15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C13:E15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C13:E15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D13:F15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D13:F15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E13:G15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E13:G15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F13:H15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F13:H15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G13:I15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G13:I15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H13:J15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H13:J15,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="AO107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I13:K15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I13:K15,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="AP107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J13:L15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J13:L15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AQ107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K13:M15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K13:M15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AR107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L13:N15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L13:N15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M13:O15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M13:O15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N13:P15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N13:P15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O13:Q15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O13:Q15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P13:R15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P13:R15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q13:S15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q13:S15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R13:T15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R13:T15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S13:U15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S13:U15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T13:V15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T13:V15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U13:W15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U13:W15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BB107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V13:X15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V13:X15,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BC107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W13:Y15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W13:Y15,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="BD107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X13:Z15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X13:Z15,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="BE107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y13:AA15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y13:AA15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z13:AB15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z13:AB15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA13:AC15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA13:AC15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB13:AD15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB13:AD15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI107" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC13:AE15,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC13:AE15,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -19824,115 +19824,115 @@
         <v>0</v>
       </c>
       <c r="AH108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B14:D16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B14:D16,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C14:E16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C14:E16,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D14:F16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D14:F16,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E14:G16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E14:G16,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F14:H16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F14:H16,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G14:I16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G14:I16,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AN108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H14:J16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H14:J16,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="AO108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I14:K16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I14:K16,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="AP108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J14:L16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J14:L16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AQ108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K14:M16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K14:M16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AR108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L14:N16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L14:N16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M14:O16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M14:O16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N14:P16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N14:P16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O14:Q16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O14:Q16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P14:R16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P14:R16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q14:S16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q14:S16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R14:T16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R14:T16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S14:U16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S14:U16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T14:V16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T14:V16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U14:W16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U14:W16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BB108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V14:X16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V14:X16,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BC108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W14:Y16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W14:Y16,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="BD108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X14:Z16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X14:Z16,$AK$16:$AM$18)/$AK$20))</f>
         <v>113.333333333333</v>
       </c>
       <c r="BE108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y14:AA16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y14:AA16,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="BF108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z14:AB16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z14:AB16,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA14:AC16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA14:AC16,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB14:AD16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB14:AD16,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI108" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC14:AE16,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC14:AE16,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -20050,115 +20050,115 @@
         <v>0</v>
       </c>
       <c r="AH109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B15:D17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B15:D17,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C15:E17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C15:E17,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D15:F17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D15:F17,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E15:G17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E15:G17,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F15:H17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F15:H17,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G15:I17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G15:I17,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AN109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H15:J17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H15:J17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AO109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I15:K17,$AK$16:$AM$18)/$AK$20</f>
-        <v>425</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I15:K17,$AK$16:$AM$18)/$AK$20))</f>
+        <v>255</v>
       </c>
       <c r="AP109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J15:L17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J15:L17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AQ109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K15:M17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K15:M17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AR109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L15:N17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L15:N17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M15:O17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M15:O17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N15:P17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N15:P17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O15:Q17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O15:Q17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P15:R17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P15:R17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q15:S17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q15:S17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R15:T17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R15:T17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S15:U17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S15:U17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T15:V17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T15:V17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U15:W17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U15:W17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BB109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V15:X17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V15:X17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BC109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W15:Y17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W15:Y17,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="BD109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X15:Z17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X15:Z17,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="BE109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y15:AA17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y15:AA17,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BF109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z15:AB17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z15:AB17,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA15:AC17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA15:AC17,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB15:AD17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB15:AD17,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI109" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC15:AE17,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC15:AE17,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -20276,115 +20276,115 @@
         <v>0</v>
       </c>
       <c r="AH110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B16:D18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B16:D18,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C16:E18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C16:E18,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D16:F18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D16:F18,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E16:G18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E16:G18,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F16:H18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F16:H18,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G16:I18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G16:I18,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AN110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H16:J18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H16:J18,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="AO110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I16:K18,$AK$16:$AM$18)/$AK$20</f>
-        <v>-28.3333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I16:K18,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AP110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J16:L18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J16:L18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AQ110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K16:M18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K16:M18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AR110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L16:N18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L16:N18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M16:O18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M16:O18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N16:P18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N16:P18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O16:Q18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O16:Q18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P16:R18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P16:R18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q16:S18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q16:S18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R16:T18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R16:T18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S16:U18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S16:U18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T16:V18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T16:V18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U16:W18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U16:W18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BB110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V16:X18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V16:X18,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BC110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W16:Y18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W16:Y18,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="BD110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X16:Z18,$AK$16:$AM$18)/$AK$20</f>
-        <v>-28.3333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X16:Z18,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="BE110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y16:AA18,$AK$16:$AM$18)/$AK$20</f>
-        <v>-198.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y16:AA18,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="BF110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z16:AB18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z16:AB18,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA16:AC18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA16:AC18,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB16:AD18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB16:AD18,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI110" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC16:AE18,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC16:AE18,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -20502,115 +20502,115 @@
         <v>0</v>
       </c>
       <c r="AH111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B17:D19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B17:D19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C17:E19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C17:E19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D17:F19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D17:F19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E17:G19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E17:G19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F17:H19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F17:H19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G17:I19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G17:I19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H17:J19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H17:J19,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="AO111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I17:K19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I17:K19,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="AP111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J17:L19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J17:L19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AQ111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K17:M19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K17:M19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AR111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L17:N19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L17:N19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M17:O19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M17:O19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N17:P19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N17:P19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O17:Q19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O17:Q19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P17:R19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P17:R19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q17:S19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q17:S19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R17:T19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R17:T19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S17:U19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S17:U19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T17:V19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T17:V19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U17:W19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U17:W19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BB111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V17:X19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V17:X19,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BC111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W17:Y19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W17:Y19,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="BD111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X17:Z19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X17:Z19,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="BE111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y17:AA19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y17:AA19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z17:AB19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z17:AB19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA17:AC19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA17:AC19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB17:AD19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB17:AD19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI111" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC17:AE19,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC17:AE19,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -20728,115 +20728,115 @@
         <v>0</v>
       </c>
       <c r="AH112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B18:D20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B18:D20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C18:E20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C18:E20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D18:F20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D18:F20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E18:G20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E18:G20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F18:H20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F18:H20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G18:I20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G18:I20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H18:J20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H18:J20,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="AO112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I18:K20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I18:K20,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AP112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J18:L20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J18:L20,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="AQ112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K18:M20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K18:M20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AR112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L18:N20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L18:N20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M18:O20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M18:O20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N18:P20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N18:P20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O18:Q20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O18:Q20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P18:R20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P18:R20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q18:S20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q18:S20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R18:T20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R18:T20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S18:U20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S18:U20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T18:V20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T18:V20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U18:W20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U18:W20,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BB112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V18:X20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V18:X20,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="BC112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W18:Y20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W18:Y20,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="BD112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X18:Z20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X18:Z20,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="BE112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y18:AA20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y18:AA20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z18:AB20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z18:AB20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA18:AC20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA18:AC20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB18:AD20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB18:AD20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI112" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC18:AE20,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC18:AE20,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -20954,115 +20954,115 @@
         <v>0</v>
       </c>
       <c r="AH113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B19:D21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B19:D21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C19:E21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C19:E21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D19:F21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D19:F21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E19:G21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E19:G21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F19:H21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F19:H21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G19:I21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G19:I21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H19:J21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H19:J21,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AO113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I19:K21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I19:K21,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="AP113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J19:L21,$AK$16:$AM$18)/$AK$20</f>
-        <v>-28.3333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J19:L21,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AQ113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K19:M21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K19:M21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AR113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L19:N21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L19:N21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M19:O21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M19:O21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N19:P21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N19:P21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O19:Q21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O19:Q21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P19:R21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P19:R21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q19:S21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q19:S21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R19:T21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R19:T21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S19:U21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S19:U21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T19:V21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T19:V21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U19:W21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U19:W21,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BB113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V19:X21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V19:X21,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="BC113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W19:Y21,$AK$16:$AM$18)/$AK$20</f>
-        <v>-28.3333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W19:Y21,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="BD113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X19:Z21,$AK$16:$AM$18)/$AK$20</f>
-        <v>-198.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X19:Z21,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="BE113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y19:AA21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y19:AA21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z19:AB21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z19:AB21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA19:AC21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA19:AC21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB19:AD21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB19:AD21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI113" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC19:AE21,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC19:AE21,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -21180,115 +21180,115 @@
         <v>0</v>
       </c>
       <c r="AH114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B20:D22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B20:D22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C20:E22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C20:E22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D20:F22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D20:F22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E20:G22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E20:G22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F20:H22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F20:H22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G20:I22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G20:I22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H20:J22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H20:J22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I20:K22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I20:K22,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="AP114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J20:L22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J20:L22,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AQ114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K20:M22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K20:M22,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="AR114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L20:N22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L20:N22,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AS114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M20:O22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M20:O22,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AT114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N20:P22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N20:P22,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O20:Q22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O20:Q22,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P20:R22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P20:R22,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q20:S22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q20:S22,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R20:T22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R20:T22,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S20:U22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S20:U22,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AZ114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T20:V22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T20:V22,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="BA114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U20:W22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U20:W22,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="BB114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V20:X22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V20:X22,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="BC114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W20:Y22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W20:Y22,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="BD114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X20:Z22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X20:Z22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y20:AA22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y20:AA22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z20:AB22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z20:AB22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA20:AC22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA20:AC22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB20:AD22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB20:AD22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI114" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC20:AE22,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC20:AE22,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -21406,115 +21406,115 @@
         <v>0</v>
       </c>
       <c r="AH115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B21:D23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B21:D23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C21:E23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C21:E23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D21:F23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D21:F23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E21:G23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E21:G23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F21:H23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F21:H23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G21:I23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G21:I23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H21:J23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H21:J23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I21:K23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I21:K23,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AP115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J21:L23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J21:L23,$AK$16:$AM$18)/$AK$20))</f>
         <v>56.6666666666667</v>
       </c>
       <c r="AQ115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K21:M23,$AK$16:$AM$18)/$AK$20</f>
-        <v>-85</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K21:M23,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AR115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L21:N23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L21:N23,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="AS115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M21:O23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M21:O23,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="AT115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N21:P23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N21:P23,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AU115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O21:Q23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O21:Q23,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AV115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P21:R23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P21:R23,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AW115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q21:S23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q21:S23,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AX115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R21:T23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R21:T23,$AK$16:$AM$18)/$AK$20))</f>
         <v>255</v>
       </c>
       <c r="AY115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S21:U23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S21:U23,$AK$16:$AM$18)/$AK$20))</f>
         <v>226.666666666667</v>
       </c>
       <c r="AZ115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T21:V23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T21:V23,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="BA115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U21:W23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U21:W23,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="BB115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V21:X23,$AK$16:$AM$18)/$AK$20</f>
-        <v>-56.6666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V21:X23,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="BC115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W21:Y23,$AK$16:$AM$18)/$AK$20</f>
-        <v>-198.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W21:Y23,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="BD115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X21:Z23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X21:Z23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y21:AA23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y21:AA23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z21:AB23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z21:AB23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA21:AC23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA21:AC23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB21:AD23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB21:AD23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI115" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC21:AE23,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC21:AE23,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -21632,115 +21632,115 @@
         <v>0</v>
       </c>
       <c r="AH116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B22:D24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B22:D24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C22:E24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C22:E24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D22:F24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D22:F24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E22:G24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E22:G24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F22:H24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F22:H24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G22:I24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G22:I24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H22:J24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H22:J24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I22:K24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I22:K24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J22:L24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J22:L24,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AQ116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K22:M24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K22:M24,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AR116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L22:N24,$AK$16:$AM$18)/$AK$20</f>
-        <v>-141.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L22:N24,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AS116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M22:O24,$AK$16:$AM$18)/$AK$20</f>
-        <v>-85</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M22:O24,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AT116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N22:P24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N22:P24,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="AU116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O22:Q24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O22:Q24,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="AV116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P22:R24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P22:R24,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="AW116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q22:S24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q22:S24,$AK$16:$AM$18)/$AK$20))</f>
         <v>198.333333333333</v>
       </c>
       <c r="AX116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R22:T24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R22:T24,$AK$16:$AM$18)/$AK$20))</f>
         <v>170</v>
       </c>
       <c r="AY116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S22:U24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S22:U24,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AZ116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T22:V24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T22:V24,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="BA116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U22:W24,$AK$16:$AM$18)/$AK$20</f>
-        <v>-311.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U22:W24,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="BB116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V22:X24,$AK$16:$AM$18)/$AK$20</f>
-        <v>-198.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V22:X24,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="BC116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W22:Y24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W22:Y24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X22:Z24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X22:Z24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y22:AA24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y22:AA24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z22:AB24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z22:AB24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA22:AC24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA22:AC24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB22:AD24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB22:AD24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI116" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC22:AE24,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC22:AE24,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -21858,115 +21858,115 @@
         <v>0</v>
       </c>
       <c r="AH117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B23:D25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B23:D25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C23:E25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C23:E25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D23:F25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D23:F25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E23:G25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E23:G25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F23:H25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F23:H25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G23:I25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G23:I25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H23:J25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H23:J25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I23:K25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I23:K25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J23:L25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J23:L25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K23:M25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K23:M25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L23:N25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L23:N25,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AS117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M23:O25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M23:O25,$AK$16:$AM$18)/$AK$20))</f>
         <v>28.3333333333333</v>
       </c>
       <c r="AT117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N23:P25,$AK$16:$AM$18)/$AK$20</f>
-        <v>-170</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N23:P25,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AU117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O23:Q25,$AK$16:$AM$18)/$AK$20</f>
-        <v>-141.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O23:Q25,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AV117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P23:R25,$AK$16:$AM$18)/$AK$20</f>
-        <v>-113.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P23:R25,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AW117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q23:S25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q23:S25,$AK$16:$AM$18)/$AK$20))</f>
         <v>85</v>
       </c>
       <c r="AX117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R23:T25,$AK$16:$AM$18)/$AK$20</f>
-        <v>-170</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R23:T25,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AY117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S23:U25,$AK$16:$AM$18)/$AK$20</f>
-        <v>-311.666666666667</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S23:U25,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AZ117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T23:V25,$AK$16:$AM$18)/$AK$20</f>
-        <v>-198.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T23:V25,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="BA117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U23:W25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U23:W25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V23:X25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V23:X25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W23:Y25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W23:Y25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X23:Z25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X23:Z25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y23:AA25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y23:AA25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z23:AB25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z23:AB25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA23:AC25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA23:AC25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB23:AD25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB23:AD25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI117" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC23:AE25,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC23:AE25,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -22084,115 +22084,115 @@
         <v>0</v>
       </c>
       <c r="AH118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B24:D26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B24:D26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C24:E26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C24:E26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D24:F26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D24:F26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E24:G26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E24:G26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F24:H26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F24:H26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G24:I26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G24:I26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H24:J26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H24:J26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I24:K26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I24:K26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J24:L26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J24:L26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K24:M26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K24:M26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L24:N26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L24:N26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M24:O26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M24:O26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N24:P26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N24:P26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O24:Q26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O24:Q26,$AK$16:$AM$18)/$AK$20))</f>
         <v>141.666666666667</v>
       </c>
       <c r="AV118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P24:R26,$AK$16:$AM$18)/$AK$20</f>
-        <v>-113.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P24:R26,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AW118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q24:S26,$AK$16:$AM$18)/$AK$20</f>
-        <v>-198.333333333333</v>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q24:S26,$AK$16:$AM$18)/$AK$20))</f>
+        <v>0</v>
       </c>
       <c r="AX118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R24:T26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R24:T26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S24:U26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S24:U26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T24:V26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T24:V26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U24:W26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U24:W26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V24:X26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V24:X26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W24:Y26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W24:Y26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X24:Z26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X24:Z26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y24:AA26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y24:AA26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z24:AB26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z24:AB26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA24:AC26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA24:AC26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB24:AD26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB24:AD26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI118" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC24:AE26,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC24:AE26,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -22310,115 +22310,115 @@
         <v>0</v>
       </c>
       <c r="AH119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B25:D27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B25:D27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C25:E27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C25:E27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D25:F27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D25:F27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E25:G27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E25:G27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F25:H27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F25:H27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G25:I27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G25:I27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H25:J27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H25:J27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I25:K27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I25:K27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J25:L27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J25:L27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K25:M27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K25:M27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L25:N27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L25:N27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M25:O27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M25:O27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N25:P27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N25:P27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O25:Q27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O25:Q27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AV119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P25:R27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P25:R27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AW119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q25:S27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q25:S27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AX119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R25:T27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R25:T27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S25:U27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S25:U27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T25:V27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T25:V27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U25:W27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U25:W27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V25:X27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V25:X27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W25:Y27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W25:Y27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X25:Z27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X25:Z27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y25:AA27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y25:AA27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z25:AB27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z25:AB27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA25:AC27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA25:AC27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB25:AD27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB25:AD27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI119" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC25:AE27,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC25:AE27,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -22536,115 +22536,115 @@
         <v>0</v>
       </c>
       <c r="AH120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B26:D28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B26:D28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C26:E28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C26:E28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D26:F28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D26:F28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E26:G28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E26:G28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F26:H28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F26:H28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G26:I28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G26:I28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H26:J28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H26:J28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I26:K28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I26:K28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J26:L28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J26:L28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K26:M28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K26:M28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L26:N28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L26:N28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M26:O28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M26:O28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N26:P28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N26:P28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O26:Q28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O26:Q28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AV120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P26:R28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P26:R28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AW120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q26:S28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q26:S28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AX120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R26:T28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R26:T28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S26:U28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S26:U28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T26:V28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T26:V28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U26:W28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U26:W28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V26:X28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V26:X28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W26:Y28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W26:Y28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X26:Z28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X26:Z28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y26:AA28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y26:AA28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z26:AB28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z26:AB28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA26:AC28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA26:AC28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB26:AD28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB26:AD28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI120" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC26:AE28,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC26:AE28,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -22762,115 +22762,115 @@
         <v>0</v>
       </c>
       <c r="AH121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B27:D29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B27:D29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C27:E29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C27:E29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D27:F29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D27:F29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E27:G29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E27:G29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F27:H29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F27:H29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G27:I29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G27:I29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H27:J29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H27:J29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I27:K29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I27:K29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J27:L29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J27:L29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K27:M29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K27:M29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L27:N29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L27:N29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M27:O29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M27:O29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N27:P29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N27:P29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O27:Q29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O27:Q29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AV121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P27:R29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P27:R29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AW121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q27:S29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q27:S29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AX121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R27:T29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R27:T29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S27:U29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S27:U29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T27:V29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T27:V29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U27:W29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U27:W29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V27:X29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V27:X29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W27:Y29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W27:Y29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X27:Z29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X27:Z29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y27:AA29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y27:AA29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z27:AB29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z27:AB29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA27:AC29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA27:AC29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB27:AD29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB27:AD29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI121" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC27:AE29,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC27:AE29,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -22988,115 +22988,115 @@
         <v>0</v>
       </c>
       <c r="AH122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B28:D30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B28:D30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C28:E30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C28:E30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D28:F30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D28:F30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E28:G30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E28:G30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F28:H30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F28:H30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G28:I30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G28:I30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H28:J30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H28:J30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I28:K30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I28:K30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J28:L30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J28:L30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K28:M30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K28:M30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L28:N30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L28:N30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M28:O30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M28:O30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N28:P30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N28:P30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O28:Q30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O28:Q30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AV122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P28:R30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P28:R30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AW122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q28:S30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q28:S30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AX122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R28:T30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R28:T30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S28:U30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S28:U30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T28:V30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T28:V30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U28:W30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U28:W30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V28:X30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V28:X30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W28:Y30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W28:Y30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X28:Z30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X28:Z30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y28:AA30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y28:AA30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z28:AB30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z28:AB30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA28:AC30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA28:AC30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB28:AD30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB28:AD30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI122" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC28:AE30,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC28:AE30,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
@@ -23214,115 +23214,115 @@
         <v>0</v>
       </c>
       <c r="AH123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(B29:D31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(B29:D31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AI123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(C29:E31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(C29:E31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AJ123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(D29:F31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(D29:F31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AK123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(E29:G31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(E29:G31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AL123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(F29:H31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(F29:H31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AM123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(G29:I31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(G29:I31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AN123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(H29:J31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(H29:J31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AO123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(I29:K31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(I29:K31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AP123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(J29:L31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(J29:L31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AQ123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(K29:M31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(K29:M31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AR123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(L29:N31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(L29:N31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AS123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(M29:O31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(M29:O31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AT123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(N29:P31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(N29:P31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AU123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(O29:Q31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(O29:Q31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AV123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(P29:R31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(P29:R31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AW123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Q29:S31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Q29:S31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AX123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(R29:T31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(R29:T31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AY123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(S29:U31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(S29:U31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="AZ123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(T29:V31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(T29:V31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BA123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(U29:W31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(U29:W31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BB123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(V29:X31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(V29:X31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BC123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(W29:Y31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(W29:Y31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BD123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(X29:Z31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(X29:Z31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BE123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Y29:AA31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Y29:AA31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BF123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(Z29:AB31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(Z29:AB31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BG123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AA29:AC31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AA29:AC31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BH123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AB29:AD31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AB29:AD31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
       <c r="BI123" s="13" t="n">
-        <f aca="false">SUMPRODUCT(AC29:AE31,$AK$16:$AM$18)/$AK$20</f>
+        <f aca="false">MIN(255,MAX(0,SUMPRODUCT(AC29:AE31,$AK$16:$AM$18)/$AK$20))</f>
         <v>0</v>
       </c>
     </row>
